--- a/data/dividends_info_20261003.xlsx
+++ b/data/dividends_info_20261003.xlsx
@@ -1580,7 +1580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C105"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1705,7 +1705,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1715,14 +1715,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1749,14 +1749,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1773,7 +1773,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1783,14 +1783,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1800,14 +1800,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1824,7 +1824,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1834,14 +1834,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1858,7 +1858,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1875,7 +1875,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1885,14 +1885,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1909,7 +1909,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1919,14 +1919,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1943,7 +1943,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2062,7 +2062,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2072,14 +2072,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2089,14 +2089,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2113,7 +2113,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,14 +2123,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2157,14 +2157,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2174,14 +2174,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2191,14 +2191,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2208,14 +2208,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2232,7 +2232,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2242,14 +2242,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2259,14 +2259,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2276,14 +2276,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2300,7 +2300,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2310,14 +2310,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2327,14 +2327,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2351,7 +2351,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2361,14 +2361,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2378,14 +2378,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2402,7 +2402,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2412,14 +2412,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2453,7 +2453,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2463,14 +2463,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2497,14 +2497,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2514,14 +2514,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2531,14 +2531,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2589,7 +2589,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2606,7 +2606,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2623,7 +2623,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2674,7 +2674,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2684,14 +2684,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>LANDI RENZO S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2718,14 +2718,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LANDI RENZO S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2735,14 +2735,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2759,7 +2759,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2820,14 +2820,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2844,7 +2844,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2854,14 +2854,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2871,14 +2871,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2888,14 +2888,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2905,14 +2905,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2929,7 +2929,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2939,14 +2939,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2990,14 +2990,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3007,14 +3007,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3041,14 +3041,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3065,7 +3065,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3082,7 +3082,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3099,7 +3099,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3116,7 +3116,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3126,14 +3126,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3150,7 +3150,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3167,7 +3167,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3177,14 +3177,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3201,7 +3201,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3211,14 +3211,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3228,14 +3228,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3252,7 +3252,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3262,14 +3262,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3295,74 +3295,6 @@
         </is>
       </c>
       <c r="C101" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Basic Net S.p.A.</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>BIESSE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Lottomatica Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
         <is>
           <t>Additional Periodic Financial Information</t>
         </is>
@@ -3392,44 +3324,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Lottomatica Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>